--- a/test/fixtures/headers-no-send-outlet.xlsx
+++ b/test/fixtures/headers-no-send-outlet.xlsx
@@ -193,7 +193,7 @@
     <t xml:space="preserve">2026-10-10 07:30:00</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-09 23:50:00</t>
+    <t xml:space="preserve">2026-10-10 06:50:00</t>
   </si>
   <si>
     <t xml:space="preserve">10000000000006</t>

--- a/test/fixtures/headers-no-send-outlet.xlsx
+++ b/test/fixtures/headers-no-send-outlet.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t xml:space="preserve">scan order number</t>
   </si>
@@ -407,6 +407,12 @@
   </si>
   <si>
     <t xml:space="preserve">855123456718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s000000018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10 08:19:00</t>
   </si>
 </sst>
 </file>
@@ -2195,6 +2201,71 @@
         <v>38</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
+        <v>133</v>
+      </c>
+      <c r="B29" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s" s="1">
+        <v>134</v>
+      </c>
+      <c r="E29" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="F29" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="G29" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="H29" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="I29" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="J29" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>0.5</v>
+      </c>
+      <c r="M29">
+        <v>0.5</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="Q29" t="s" s="1">
+        <v>131</v>
+      </c>
+      <c r="R29" t="s" s="1">
+        <v>132</v>
+      </c>
+      <c r="S29" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="X29" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="Y29" t="s" s="1">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>